--- a/pacjenci/JANUSZ FRONT.xlsx
+++ b/pacjenci/JANUSZ FRONT.xlsx
@@ -534,7 +534,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Do oceny</t>
+          <t>Brak aktywnej choroby</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -542,17 +542,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>CR</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>4 - utrzymujący się wychwyt patologiczny</t>
+          <t>3 - wychwyt nie większy niż wątroba</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Stabilizacja choroby. Klasyfikacja Lugano: Stable Disease (SD) - stabilizacja choroby. Deauville: 4 - utrzymujący się wychwyt patologiczny.</t>
+          <t>Nie stwierdza się aktywnej metabolicznie choroby. Klasyfikacja Lugano: Complete Response (CR) - całkowita odpowiedź na leczenie. Deauville: 3 - wychwyt nie większy niż wątroba.</t>
         </is>
       </c>
     </row>

--- a/pacjenci/JANUSZ FRONT.xlsx
+++ b/pacjenci/JANUSZ FRONT.xlsx
@@ -413,147 +413,110 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J3"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
+          <t>Nr badania</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
           <t>Data badania</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Nr badania</t>
-        </is>
-      </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Etap leczenia</t>
+          <t>Problem kliniczny</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>Linia leczenia</t>
+          <t>Zakres badania</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Rozpoznanie</t>
+          <t>Opis badania</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>Opis</t>
+          <t>Wnioski</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
           <t>SUVmax</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>Ocena odpowiedzi</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>Deauville</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>Wnioski</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
         <is>
           <t>14.06.2021</t>
         </is>
       </c>
-      <c r="B2" t="n">
-        <v>1</v>
-      </c>
       <c r="C2" t="inlineStr">
         <is>
           <t>Chłoniak DLBCL NOS na podstawie badania hist-pat guza jelita cienkiego, jelita grubego i dna pęcherza. W dniach 23.03.2021-16.04.2021 wykopano zabieg resekcji guza z otrzewną, fragmentem esicy, 30 cm odcinkiem jelita krętego oraz ze szczytem pęcherza moczowego.  OPIS: Ibraheem Al Maraih</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr"/>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>od szczytu głowy do 1/3 ud Akwizycję przeprowadzono  po 56 min od podania 18F-FDG. Glikemia: 90mmol/l</t>
+        </is>
+      </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>DLBCL</t>
+          <t>: Ubytek metabolizmu w prawej półkuli móżdżku w topografii hypodensyjnego obszaru wielkości 35x36mm - poudarowego? Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi.  Klatka piersiowa i śródpiersie: Fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Niewielkie zmiany włókniste w szczytach obu płucach. Uwypuklenie łuku aorty lewobocznie wielkości 20x26mm - do ew. oceny w badaniu angio-TK aorty piersiowej.  Brzuch i miednica: Liczne spakietowane i pojedyncze aktywne metabolicznie węzły chłonne krezkowe od wysokości trzonów kręgów L1 do L4  wielkości wg PET do 67x32x31mm, SUV max do 21 [Im fuz 187] Rozlane i ogniskowe aktywne metaboliczne obszary w pętlach jelitowych średnicy wg PET do 12mm, SUV max do 5,6 [Im fuz 194] -  ogniska procesu chłoniakowego? Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy.  Układ kostny: Fizjologiczny metabolizm FDG w układzie kostnym. Zmiany zwyrodnieniowo-wytwórcze kręgosłupa; dyskopatie w odcinku lędźwiowym. Drobna wyspa kostna  w talerzu kości biodrowej prawej.  Inne: Miażdżyca aorty i tętnic potomnych.   Wartości referencyjne: MBPS SUVmax 1,9, Prawy płat wątroby SUVmax do 2,7.</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Do oceny</t>
+          <t>Badaniem PET/CT z 18F-FDG uwidoczniono aktywne metabolicznie węzły chłonne krezkowe. Nie można wykluczyć zajęcia pętli jelitowych - jak w opisie powyżej.</t>
         </is>
       </c>
       <c r="G2" t="n">
         <v>5.6</v>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>Baseline</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>Nie dotyczy</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>Aktywna metabolicznie choroba przed rozpoczęciem leczenia. Badanie wyjściowe stanowiące punkt odniesienia.</t>
-        </is>
-      </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
         <is>
           <t>28.09.2021</t>
         </is>
       </c>
-      <c r="B3" t="n">
-        <v>2</v>
-      </c>
       <c r="C3" t="inlineStr">
         <is>
           <t>Chłoniak DLBCL NOS na podstawie badania hist-pat guza jelita cienkiego, jelita grubego i dna pęcherza. Ocena remisji choroby po 3 cyklach chth.</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>od szczytu głowy do 1/3 ud. Akwizycję przeprowadzono  po 58 min od podania 18F-FDG. Glikemia: 108mg%.</t>
+        </is>
+      </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>DLBCL</t>
+          <t>: Ubytek metabolizmu w prawej półkuli móżdżku w topografii hypodensyjnego w przeglądowym badaniu TK obszaru wielkości 35x36mm - torbiel pajęczynówki? porencefalia poudarowa? Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Komory boczne mózgu poszerzone - zanik podkorowy mózgu. Wydatne zwapnienie w przedniej części sierpu mózgu. Drobne torbielki ze zwapniałymi ścianami w splotach naczyniastych rogów potylicznych komór bocznych. Hypoplazja zatok czołowych. Ząb zatrzymany w obrębie kości szczękowej po stronie prawej.  Klatka piersiowa i śródpiersie: Fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Tętniakowate poszerzenie do 22mm t. podobojczykowej lewej w części przyaortalnej oraz tętniakowate uwypuklenie łuku aorty na stronę lewą, wielkości 25x28mm - do oceny w badaniu angio-TK. Odcinkowe pogrubienie osierdzia od strony PP - do kontroli w Echokardiografii. Węzeł chłonny przytchawiczy dolny prawy wielkości 17x9mm. Poza tym dość liczne węzły chłonne przytchawicze i śródpiersiowe wielkości do 11mm. Niewielkie zmiany włókniste w szczytach obu płucach. Nieregularny obszar o typie "mlecznej szyby" wielkości ok. 45x60mm, ze zwłóknieniami widoczny jest nadprzeponowo w segm. 8 i nieco 9 płuca lewego. Niewielkie zmiany włókniste obustronnie nadprzeponowo.  Brzuch i miednica: Rozlane i ogniskowe pobudzenie metaboliczne w pętlach jelitowych, zwłaszcza w kątnicy - czynnościowo? - do ew. kontroli w kolonoskopii. Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Drobne i wydatne uwapnione konkrementy w pęcherzyku żółciowym. Nerki o nieco "pozaciąganych" pozapalnie obrysach. Prostata powiększona - do kontroli urologicznej. Liczne flebolity w miednicy mniejszej. Węzły chłonne pachwinowe obustronnie wielkości do 12mm.  Układ kostny: Zmiany zwyrodnieniowo-wytwórcze kręgosłupa odcinkowo z pobudzeniem metabolicznym. Poza tym fizjologiczny metabolizm FDG w układzie kostnym. Zmiany zwyrodnieniowo-wytwórcze kręgosłupa. Niewielka prawowypukła skolioza kręgosłupa piersiowego. Dyskopatie w odcinku lędźwiowym kręgosłupa. Os sacrum arcuatum. Zmiany zwyrodnieniowo-wytwórcze w małych stawach międzykręgowych [nasilone w odcinku lędźwiowym oraz szyjnym kręgosłupa] i w stawach żebrowo-poprzecznych. Nieregularne obrysy przyśrodkowej części głowy prawej kości udowej, z pogrubieniem i rozwarstwieniem blaszki zewnętrznej. Drobna wyspa kostna  w talerzu kości biodrowej prawej.  Inne: Miażdżyca aorty i tętnic potomnych.   Wartości referencyjne: MBPS SUVmax do 2,5; Prawy płat wątroby SUVmax do 3,5.</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Brak aktywnej choroby</t>
+          <t>Badaniem PET/CT z 18F-FDG nie uwidoczniono obecności aktywnego metabolicznie procesu chłoniakowego. Poza tym jak w opisie powyżej.   28,12,2021 Akwizycję przeprowadzono  po 58min od podania 18F-FDG. Glikemia: 149mg%. Problem kliniczny:  Chłoniak DLBCL. Ocena remisji choroby.   Konsultujący specjalista radiologii i diagnostyki obrazowej: A. Grochowska  Głowa i szyja: Ubytek metabolizmu w prawej półkuli móżdżku w topografii hypodensyjnego w przeglądowym badaniu TK obszaru wielkości ok 37x30mm - torbiel pajęczynówki? porencefalia poudarowa? Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Komory boczne mózgu poszerzone - zanik podkorowy mózgu. Wydatne zwapnienie w przedniej części sierpu mózgu. Drobne torbielki ze zwapniałymi ścianami w splotach naczyniastych rogów potylicznych komór bocznych. Hypoplazja zatok czołowych. Ząb zatrzymany w obrębie kości szczękowej po stronie prawej.  Klatka piersiowa i śródpiersie: Fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Stan po stentowaniu aorty piersiowej, tętniakowate poszerzenie do 20mm t. podobojczykowej lewej w części przyaortalnej oraz tętniakowate uwypuklenie łuku aorty na stronę lewą, wielkości 25x29mm. Węzeł chłonny przytchawiczy dolny prawy wielkości 18x9mm. Poza tym nieliczne węzły chłonne przytchawicze i śródpiersiowe wielkości do 11mm. Niewielkie zmiany włókniste w szczytach obu płucach. Niewielkie zmiany włókniste obustronnie nadprzeponowo. Guzek średnicy ok. 7 mm w segmencie 8/9 płuca lewego - do kontroli.   Brzuch i miednica: Pobudzenie metaboliczne przy naczyniach udowych w pachwinie prawej - węzeł chłonny/procesy gojenia ? SUV max 4,0 [lm fuz 256] Rozlane i ogniskowe pobudzenie metaboliczne w pętlach jelitowych - czynnościowo? - do ew. kontroli w kolonoskopii. Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Uwapnione konkrementy w pęcherzyku żółciowym średnicy do 10mm. Nerki o nieco "pozaciąganych" pozapalnie obrysach. Prostata powiększona - do kontroli urologicznej. Liczne flebolity w miednicy mniejszej. Węzły chłonne pachwinowe obustronnie wielkości do 12mm.  Układ kostny: Zmiany zwyrodnieniowo-wytwórcze kręgosłupa odcinkowo z pobudzeniem metabolicznym. Poza tym fizjologiczny metabolizm FDG w układzie kostnym. Zmiany zwyrodnieniowo-wytwórcze kręgosłupa. Niewielka prawowypukła skolioza kręgosłupa piersiowego. Dyskopatie w odcinku lędźwiowym kręgosłupa. Os sacrum arcuatum. Zmiany zwyrodnieniowo-wytwórcze w małych stawach międzykręgowych [nasilone w odcinku lędźwiowym oraz szyjnym kręgosłupa] i w stawach żebrowo-poprzecznych. Stan po kilkupoziomowym złamaniu żeber prawych w odcinkach bocznych. Nieregularne obrysy przyśrodkowej części głowy prawej kości udowej, z pogrubieniem i rozwarstwieniem blaszki zewnętrznej. Drobna wyspa kostna  w talerzu kości biodrowej prawej.  Inne: Miażdżyca aorty i tętnic potomnych.   Wartości referencyjne: MBPS SUVmax do 2,5; Prawy płat wątroby SUVmax do 3,5.  Wnioski:  Badaniem PET/CT z 18F-FDG nie uwidoczniono jednoznacznych cech obecności aktywnego metabolicznie procesu chłoniakowego. Uwidoczniono pobudzenie metaboliczne przy naczyniach udowych w pachwinie prawej - węzeł chłonny/procesy gojenia - do oceny klinicznej/kontroli. Poza tym jak w opisie powyżej.</t>
         </is>
       </c>
       <c r="G3" t="n">
         <v>4</v>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>CR</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>3 - wychwyt nie większy niż wątroba</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>Nie stwierdza się aktywnej metabolicznie choroby. Klasyfikacja Lugano: Complete Response (CR) - całkowita odpowiedź na leczenie. Deauville: 3 - wychwyt nie większy niż wątroba.</t>
-        </is>
       </c>
     </row>
   </sheetData>

--- a/pacjenci/JANUSZ FRONT.xlsx
+++ b/pacjenci/JANUSZ FRONT.xlsx
@@ -413,13 +413,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:L3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Nr badania</t>
+          <t>Nr PET</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -439,17 +439,42 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Opis badania</t>
+          <t>Glikemia</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
+          <t>Czas po FDG</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Głowa i szyja</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Klatka piersiowa</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Brzuch i miednica</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>Układ kostny</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
           <t>Wnioski</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>SUVmax</t>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>SUVmax_global</t>
         </is>
       </c>
     </row>
@@ -469,20 +494,45 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>od szczytu głowy do 1/3 ud Akwizycję przeprowadzono  po 56 min od podania 18F-FDG. Glikemia: 90mmol/l</t>
+          <t>od szczytu głowy do 1/3 ud</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>: Ubytek metabolizmu w prawej półkuli móżdżku w topografii hypodensyjnego obszaru wielkości 35x36mm - poudarowego? Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi.  Klatka piersiowa i śródpiersie: Fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Niewielkie zmiany włókniste w szczytach obu płucach. Uwypuklenie łuku aorty lewobocznie wielkości 20x26mm - do ew. oceny w badaniu angio-TK aorty piersiowej.  Brzuch i miednica: Liczne spakietowane i pojedyncze aktywne metabolicznie węzły chłonne krezkowe od wysokości trzonów kręgów L1 do L4  wielkości wg PET do 67x32x31mm, SUV max do 21 [Im fuz 187] Rozlane i ogniskowe aktywne metaboliczne obszary w pętlach jelitowych średnicy wg PET do 12mm, SUV max do 5,6 [Im fuz 194] -  ogniska procesu chłoniakowego? Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy.  Układ kostny: Fizjologiczny metabolizm FDG w układzie kostnym. Zmiany zwyrodnieniowo-wytwórcze kręgosłupa; dyskopatie w odcinku lędźwiowym. Drobna wyspa kostna  w talerzu kości biodrowej prawej.  Inne: Miażdżyca aorty i tętnic potomnych.   Wartości referencyjne: MBPS SUVmax 1,9, Prawy płat wątroby SUVmax do 2,7.</t>
+          <t>90</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Ubytek metabolizmu w prawej półkuli móżdżku w topografii hypodensyjnego obszaru wielkości 35x36mm - poudarowego? Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi.</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Niewielkie zmiany włókniste w szczytach obu płucach. Uwypuklenie łuku aorty lewobocznie wielkości 20x26mm - do ew. oceny w badaniu angio-TK aorty piersiowej.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Liczne spakietowane i pojedyncze aktywne metabolicznie węzły chłonne krezkowe od wysokości trzonów kręgów L1 do L4  wielkości wg PET do 67x32x31mm, SUV max do 21 [Im fuz 187] Rozlane i ogniskowe aktywne metaboliczne obszary w pętlach jelitowych średnicy wg PET do 12mm, SUV max do 5,6 [Im fuz 194] -  ogniska procesu chłoniakowego? Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy.</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Fizjologiczny metabolizm FDG w układzie kostnym. Zmiany zwyrodnieniowo-wytwórcze kręgosłupa; dyskopatie w odcinku lędźwiowym. Drobna wyspa kostna  w talerzu kości biodrowej prawej.  Inne: Miażdżyca aorty i tętnic potomnych.</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
           <t>Badaniem PET/CT z 18F-FDG uwidoczniono aktywne metabolicznie węzły chłonne krezkowe. Nie można wykluczyć zajęcia pętli jelitowych - jak w opisie powyżej.</t>
         </is>
       </c>
-      <c r="G2" t="n">
+      <c r="L2" t="n">
         <v>5.6</v>
       </c>
     </row>
@@ -502,20 +552,45 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>od szczytu głowy do 1/3 ud. Akwizycję przeprowadzono  po 58 min od podania 18F-FDG. Glikemia: 108mg%.</t>
+          <t>od szczytu głowy do 1/3 ud.</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>: Ubytek metabolizmu w prawej półkuli móżdżku w topografii hypodensyjnego w przeglądowym badaniu TK obszaru wielkości 35x36mm - torbiel pajęczynówki? porencefalia poudarowa? Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Komory boczne mózgu poszerzone - zanik podkorowy mózgu. Wydatne zwapnienie w przedniej części sierpu mózgu. Drobne torbielki ze zwapniałymi ścianami w splotach naczyniastych rogów potylicznych komór bocznych. Hypoplazja zatok czołowych. Ząb zatrzymany w obrębie kości szczękowej po stronie prawej.  Klatka piersiowa i śródpiersie: Fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Tętniakowate poszerzenie do 22mm t. podobojczykowej lewej w części przyaortalnej oraz tętniakowate uwypuklenie łuku aorty na stronę lewą, wielkości 25x28mm - do oceny w badaniu angio-TK. Odcinkowe pogrubienie osierdzia od strony PP - do kontroli w Echokardiografii. Węzeł chłonny przytchawiczy dolny prawy wielkości 17x9mm. Poza tym dość liczne węzły chłonne przytchawicze i śródpiersiowe wielkości do 11mm. Niewielkie zmiany włókniste w szczytach obu płucach. Nieregularny obszar o typie "mlecznej szyby" wielkości ok. 45x60mm, ze zwłóknieniami widoczny jest nadprzeponowo w segm. 8 i nieco 9 płuca lewego. Niewielkie zmiany włókniste obustronnie nadprzeponowo.  Brzuch i miednica: Rozlane i ogniskowe pobudzenie metaboliczne w pętlach jelitowych, zwłaszcza w kątnicy - czynnościowo? - do ew. kontroli w kolonoskopii. Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Drobne i wydatne uwapnione konkrementy w pęcherzyku żółciowym. Nerki o nieco "pozaciąganych" pozapalnie obrysach. Prostata powiększona - do kontroli urologicznej. Liczne flebolity w miednicy mniejszej. Węzły chłonne pachwinowe obustronnie wielkości do 12mm.  Układ kostny: Zmiany zwyrodnieniowo-wytwórcze kręgosłupa odcinkowo z pobudzeniem metabolicznym. Poza tym fizjologiczny metabolizm FDG w układzie kostnym. Zmiany zwyrodnieniowo-wytwórcze kręgosłupa. Niewielka prawowypukła skolioza kręgosłupa piersiowego. Dyskopatie w odcinku lędźwiowym kręgosłupa. Os sacrum arcuatum. Zmiany zwyrodnieniowo-wytwórcze w małych stawach międzykręgowych [nasilone w odcinku lędźwiowym oraz szyjnym kręgosłupa] i w stawach żebrowo-poprzecznych. Nieregularne obrysy przyśrodkowej części głowy prawej kości udowej, z pogrubieniem i rozwarstwieniem blaszki zewnętrznej. Drobna wyspa kostna  w talerzu kości biodrowej prawej.  Inne: Miażdżyca aorty i tętnic potomnych.   Wartości referencyjne: MBPS SUVmax do 2,5; Prawy płat wątroby SUVmax do 3,5.</t>
+          <t>108</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Ubytek metabolizmu w prawej półkuli móżdżku w topografii hypodensyjnego w przeglądowym badaniu TK obszaru wielkości 35x36mm - torbiel pajęczynówki? porencefalia poudarowa? Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Komory boczne mózgu poszerzone - zanik podkorowy mózgu. Wydatne zwapnienie w przedniej części sierpu mózgu. Drobne torbielki ze zwapniałymi ścianami w splotach naczyniastych rogów potylicznych komór bocznych. Hypoplazja zatok czołowych. Ząb zatrzymany w obrębie kości szczękowej po stronie prawej.</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Tętniakowate poszerzenie do 22mm t. podobojczykowej lewej w części przyaortalnej oraz tętniakowate uwypuklenie łuku aorty na stronę lewą, wielkości 25x28mm - do oceny w badaniu angio-TK. Odcinkowe pogrubienie osierdzia od strony PP - do kontroli w Echokardiografii. Węzeł chłonny przytchawiczy dolny prawy wielkości 17x9mm. Poza tym dość liczne węzły chłonne przytchawicze i śródpiersiowe wielkości do 11mm. Niewielkie zmiany włókniste w szczytach obu płucach. Nieregularny obszar o typie "mlecznej szyby" wielkości ok. 45x60mm, ze zwłóknieniami widoczny jest nadprzeponowo w segm. 8 i nieco 9 płuca lewego. Niewielkie zmiany włókniste obustronnie nadprzeponowo.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Rozlane i ogniskowe pobudzenie metaboliczne w pętlach jelitowych, zwłaszcza w kątnicy - czynnościowo? - do ew. kontroli w kolonoskopii. Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Drobne i wydatne uwapnione konkrementy w pęcherzyku żółciowym. Nerki o nieco "pozaciąganych" pozapalnie obrysach. Prostata powiększona - do kontroli urologicznej. Liczne flebolity w miednicy mniejszej. Węzły chłonne pachwinowe obustronnie wielkości do 12mm.</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Zmiany zwyrodnieniowo-wytwórcze kręgosłupa odcinkowo z pobudzeniem metabolicznym. Poza tym fizjologiczny metabolizm FDG w układzie kostnym. Zmiany zwyrodnieniowo-wytwórcze kręgosłupa. Niewielka prawowypukła skolioza kręgosłupa piersiowego. Dyskopatie w odcinku lędźwiowym kręgosłupa. Os sacrum arcuatum. Zmiany zwyrodnieniowo-wytwórcze w małych stawach międzykręgowych [nasilone w odcinku lędźwiowym oraz szyjnym kręgosłupa] i w stawach żebrowo-poprzecznych. Nieregularne obrysy przyśrodkowej części głowy prawej kości udowej, z pogrubieniem i rozwarstwieniem blaszki zewnętrznej. Drobna wyspa kostna  w talerzu kości biodrowej prawej.  Inne: Miażdżyca aorty i tętnic potomnych.</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
           <t>Badaniem PET/CT z 18F-FDG nie uwidoczniono obecności aktywnego metabolicznie procesu chłoniakowego. Poza tym jak w opisie powyżej.   28,12,2021 Akwizycję przeprowadzono  po 58min od podania 18F-FDG. Glikemia: 149mg%. Problem kliniczny:  Chłoniak DLBCL. Ocena remisji choroby.   Konsultujący specjalista radiologii i diagnostyki obrazowej: A. Grochowska  Głowa i szyja: Ubytek metabolizmu w prawej półkuli móżdżku w topografii hypodensyjnego w przeglądowym badaniu TK obszaru wielkości ok 37x30mm - torbiel pajęczynówki? porencefalia poudarowa? Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Komory boczne mózgu poszerzone - zanik podkorowy mózgu. Wydatne zwapnienie w przedniej części sierpu mózgu. Drobne torbielki ze zwapniałymi ścianami w splotach naczyniastych rogów potylicznych komór bocznych. Hypoplazja zatok czołowych. Ząb zatrzymany w obrębie kości szczękowej po stronie prawej.  Klatka piersiowa i śródpiersie: Fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Stan po stentowaniu aorty piersiowej, tętniakowate poszerzenie do 20mm t. podobojczykowej lewej w części przyaortalnej oraz tętniakowate uwypuklenie łuku aorty na stronę lewą, wielkości 25x29mm. Węzeł chłonny przytchawiczy dolny prawy wielkości 18x9mm. Poza tym nieliczne węzły chłonne przytchawicze i śródpiersiowe wielkości do 11mm. Niewielkie zmiany włókniste w szczytach obu płucach. Niewielkie zmiany włókniste obustronnie nadprzeponowo. Guzek średnicy ok. 7 mm w segmencie 8/9 płuca lewego - do kontroli.   Brzuch i miednica: Pobudzenie metaboliczne przy naczyniach udowych w pachwinie prawej - węzeł chłonny/procesy gojenia ? SUV max 4,0 [lm fuz 256] Rozlane i ogniskowe pobudzenie metaboliczne w pętlach jelitowych - czynnościowo? - do ew. kontroli w kolonoskopii. Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Uwapnione konkrementy w pęcherzyku żółciowym średnicy do 10mm. Nerki o nieco "pozaciąganych" pozapalnie obrysach. Prostata powiększona - do kontroli urologicznej. Liczne flebolity w miednicy mniejszej. Węzły chłonne pachwinowe obustronnie wielkości do 12mm.  Układ kostny: Zmiany zwyrodnieniowo-wytwórcze kręgosłupa odcinkowo z pobudzeniem metabolicznym. Poza tym fizjologiczny metabolizm FDG w układzie kostnym. Zmiany zwyrodnieniowo-wytwórcze kręgosłupa. Niewielka prawowypukła skolioza kręgosłupa piersiowego. Dyskopatie w odcinku lędźwiowym kręgosłupa. Os sacrum arcuatum. Zmiany zwyrodnieniowo-wytwórcze w małych stawach międzykręgowych [nasilone w odcinku lędźwiowym oraz szyjnym kręgosłupa] i w stawach żebrowo-poprzecznych. Stan po kilkupoziomowym złamaniu żeber prawych w odcinkach bocznych. Nieregularne obrysy przyśrodkowej części głowy prawej kości udowej, z pogrubieniem i rozwarstwieniem blaszki zewnętrznej. Drobna wyspa kostna  w talerzu kości biodrowej prawej.  Inne: Miażdżyca aorty i tętnic potomnych.   Wartości referencyjne: MBPS SUVmax do 2,5; Prawy płat wątroby SUVmax do 3,5.  Wnioski:  Badaniem PET/CT z 18F-FDG nie uwidoczniono jednoznacznych cech obecności aktywnego metabolicznie procesu chłoniakowego. Uwidoczniono pobudzenie metaboliczne przy naczyniach udowych w pachwinie prawej - węzeł chłonny/procesy gojenia - do oceny klinicznej/kontroli. Poza tym jak w opisie powyżej.</t>
         </is>
       </c>
-      <c r="G3" t="n">
+      <c r="L3" t="n">
         <v>4</v>
       </c>
     </row>
